--- a/snowflake_summit/Snowflake_Summit_2026_Master_Partner_Scouting.xlsx
+++ b/snowflake_summit/Snowflake_Summit_2026_Master_Partner_Scouting.xlsx
@@ -1,13 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Master Directory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Directory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summit News" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +29,15 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001B7FB8"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +60,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -589,26 +609,26 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -909,26 +929,26 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K8" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1144,22 +1164,22 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K12" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1199,26 +1219,26 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K13" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1379,26 +1399,26 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="K16" t="n">
         <v>8.5</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1504,22 +1524,22 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1559,26 +1579,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>8</v>
+      </c>
+      <c r="N19" t="n">
         <v>8.5</v>
       </c>
-      <c r="L19" t="n">
-        <v>6</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1669,26 +1689,26 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
         <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2109,22 +2129,22 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M28" t="n">
         <v>4.5</v>
       </c>
       <c r="N28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O28" t="n">
         <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>6</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2167,19 +2187,19 @@
         <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N29" t="n">
         <v>4.5</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>6</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2399,26 +2419,26 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K33" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2564,7 +2584,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K36" t="n">
         <v>8.5</v>
@@ -2573,17 +2593,17 @@
         <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O36" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3474,26 +3494,26 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
         <v>8.5</v>
       </c>
       <c r="L50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M50" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -3584,22 +3604,22 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K52" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="L52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M52" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O52" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -3969,26 +3989,26 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="L58" t="n">
         <v>6</v>
       </c>
       <c r="M58" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O58" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -4024,22 +4044,22 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="L59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M59" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -4079,26 +4099,26 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K60" t="n">
         <v>8.5</v>
       </c>
       <c r="L60" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M60" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -4209,26 +4229,26 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K62" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M62" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4374,26 +4394,26 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L65" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M65" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -4689,26 +4709,26 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K70" t="n">
         <v>8.5</v>
       </c>
       <c r="L70" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M70" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="O70" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -4744,26 +4764,26 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="K71" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L71" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M71" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N71" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="O71" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -4799,22 +4819,22 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K72" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="L72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M72" t="n">
+        <v>3</v>
+      </c>
+      <c r="N72" t="n">
         <v>4.5</v>
       </c>
-      <c r="N72" t="n">
-        <v>5</v>
-      </c>
       <c r="O72" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -4854,26 +4874,26 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K73" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O73" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -4984,26 +5004,26 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K75" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L75" t="n">
         <v>6</v>
       </c>
       <c r="M75" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="N75" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O75" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -5315,7 +5335,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>an IBM Company"</t>
+          <t>Hakkoda (an IBM Company)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5659,26 +5679,26 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K86" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="L86" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M86" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="N86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O86" t="n">
         <v>6</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -5999,26 +6019,26 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K91" t="n">
+        <v>8</v>
+      </c>
+      <c r="L91" t="n">
+        <v>9</v>
+      </c>
+      <c r="M91" t="n">
+        <v>8</v>
+      </c>
+      <c r="N91" t="n">
         <v>8.5</v>
       </c>
-      <c r="L91" t="n">
-        <v>6</v>
-      </c>
-      <c r="M91" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N91" t="n">
-        <v>5</v>
-      </c>
       <c r="O91" t="n">
-        <v>6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -6054,26 +6074,26 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="K92" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M92" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -6109,22 +6129,22 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K93" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="L93" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="M93" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O93" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -6164,26 +6184,26 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K94" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="L94" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M94" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="O94" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -6384,26 +6404,26 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K98" t="n">
         <v>8.5</v>
       </c>
       <c r="L98" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M98" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O98" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -6439,26 +6459,26 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K99" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L99" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M99" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O99" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
@@ -6494,26 +6514,26 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K100" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M100" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N100" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O100" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -6549,22 +6569,22 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K101" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="L101" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M101" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="N101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O101" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -6789,26 +6809,26 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="K105" t="n">
         <v>8.5</v>
       </c>
       <c r="L105" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M105" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="N105" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O105" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -6914,26 +6934,26 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="K107" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L107" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M107" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O107" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -6969,13 +6989,13 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K108" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="L108" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M108" t="n">
         <v>4.5</v>
@@ -6984,7 +7004,7 @@
         <v>5</v>
       </c>
       <c r="O108" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -7005,7 +7025,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>a Siemens Business"</t>
+          <t>Mendix (a Siemens Business)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7099,26 +7119,26 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K110" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L110" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M110" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N110" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O110" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -7209,22 +7229,22 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="K112" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="L112" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M112" t="n">
+        <v>4</v>
+      </c>
+      <c r="N112" t="n">
         <v>4.5</v>
       </c>
-      <c r="N112" t="n">
-        <v>5</v>
-      </c>
       <c r="O112" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -7919,26 +7939,26 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="K123" t="n">
         <v>8.5</v>
       </c>
       <c r="L123" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="M123" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N123" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O123" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -8029,22 +8049,22 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K125" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L125" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M125" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O125" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -8194,26 +8214,26 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K128" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L128" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="M128" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O128" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -8249,22 +8269,22 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K129" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="L129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M129" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N129" t="n">
         <v>5</v>
       </c>
       <c r="O129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -8359,10 +8379,10 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K131" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L131" t="n">
         <v>6</v>
@@ -8371,14 +8391,14 @@
         <v>4.5</v>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O131" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -8414,7 +8434,7 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K132" t="n">
         <v>8.5</v>
@@ -8423,17 +8443,17 @@
         <v>6</v>
       </c>
       <c r="M132" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N132" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O132" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -8524,26 +8544,26 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K134" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L134" t="n">
         <v>6</v>
       </c>
       <c r="M134" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="N134" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O134" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -8779,26 +8799,26 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K138" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="L138" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M138" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O138" t="n">
         <v>6</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -8834,26 +8854,26 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K139" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="L139" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="M139" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="N139" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="O139" t="n">
         <v>6</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -8944,26 +8964,26 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="K141" t="n">
+        <v>9</v>
+      </c>
+      <c r="L141" t="n">
+        <v>2</v>
+      </c>
+      <c r="M141" t="n">
         <v>8.5</v>
       </c>
-      <c r="L141" t="n">
-        <v>6</v>
-      </c>
-      <c r="M141" t="n">
-        <v>4.5</v>
-      </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O141" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -8999,22 +9019,22 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K142" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="L142" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M142" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N142" t="n">
         <v>5</v>
       </c>
       <c r="O142" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -9054,26 +9074,26 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="K143" t="n">
+        <v>9</v>
+      </c>
+      <c r="L143" t="n">
         <v>8.5</v>
       </c>
-      <c r="L143" t="n">
-        <v>6</v>
-      </c>
       <c r="M143" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="N143" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="O143" t="n">
-        <v>6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
@@ -9164,22 +9184,22 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="L145" t="n">
         <v>6</v>
       </c>
       <c r="M145" t="n">
+        <v>7</v>
+      </c>
+      <c r="N145" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O145" t="n">
         <v>4.5</v>
-      </c>
-      <c r="N145" t="n">
-        <v>5</v>
-      </c>
-      <c r="O145" t="n">
-        <v>6</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
@@ -9614,26 +9634,26 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K152" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="L152" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="M152" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N152" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O152" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -9819,22 +9839,22 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K155" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="L155" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M155" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N155" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O155" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
@@ -9874,22 +9894,22 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K156" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="L156" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M156" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N156" t="n">
         <v>5</v>
       </c>
       <c r="O156" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
@@ -9929,26 +9949,26 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K157" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L157" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M157" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N157" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O157" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -10369,26 +10389,26 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K164" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="L164" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M164" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="N164" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O164" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -10424,22 +10444,22 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="K165" t="n">
         <v>8.5</v>
       </c>
       <c r="L165" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M165" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N165" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O165" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
@@ -10589,26 +10609,26 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K168" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="L168" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M168" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N168" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
@@ -10714,22 +10734,22 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K170" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L170" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M170" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N170" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O170" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="P170" t="inlineStr">
         <is>
@@ -10769,26 +10789,26 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K171" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L171" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M171" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="N171" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O171" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -10894,26 +10914,26 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K173" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L173" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M173" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N173" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O173" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
@@ -11209,26 +11229,26 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K178" t="n">
         <v>8.5</v>
       </c>
       <c r="L178" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M178" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="N178" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O178" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
@@ -11467,19 +11487,19 @@
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L182" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M182" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N182" t="n">
         <v>5</v>
       </c>
       <c r="O182" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -11714,22 +11734,22 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K186" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="L186" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="M186" t="n">
+        <v>2</v>
+      </c>
+      <c r="N186" t="n">
         <v>4.5</v>
       </c>
-      <c r="N186" t="n">
-        <v>5</v>
-      </c>
       <c r="O186" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="P186" t="inlineStr">
         <is>
@@ -11824,26 +11844,26 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K188" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L188" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M188" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="N188" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O188" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -11934,26 +11954,26 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="K190" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="L190" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M190" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N190" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="O190" t="n">
         <v>6</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -12044,26 +12064,26 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K192" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="L192" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M192" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="N192" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="O192" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -12174,26 +12194,26 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="K194" t="n">
+        <v>9</v>
+      </c>
+      <c r="L194" t="n">
+        <v>7</v>
+      </c>
+      <c r="M194" t="n">
         <v>8.5</v>
       </c>
-      <c r="L194" t="n">
-        <v>6</v>
-      </c>
-      <c r="M194" t="n">
-        <v>4.5</v>
-      </c>
       <c r="N194" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O194" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -12299,26 +12319,26 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K196" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="L196" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M196" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N196" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O196" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -12354,26 +12374,26 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K197" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="L197" t="n">
         <v>6</v>
       </c>
       <c r="M197" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N197" t="n">
         <v>5</v>
       </c>
       <c r="O197" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -12454,6 +12474,4801 @@
       <c r="R198" t="inlineStr">
         <is>
           <t>https://www.snowflake.com/en/summit/ ; company website / Crunchbase / PitchBook / public filings as applicable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Relevance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Semarchy</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Semarchy at Snowflake Summit 2026: MDM as a Snowflake Native App, T. Rowe Price session</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Semarchy</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://semarchy.com/events/snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Semarchy exhibits at Booth #1301, running MDM as a Snowflake Native App; co-presents Party Master 360 session with T. Rowe Price.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MathCo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MathCo hosts 'AI and Aperitifs' invite-only event at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MathCo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://experience.mathco.com/events/mathco-ai-and-aperitifs-at-snowflake-summit-2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MathCo hosts an invite-only evening at Shelby's Rooftop on June 3 alongside Snowflake Summit 2026 to connect with data and AI leaders.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arango</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Arango Showcases Live Contextual Data Layer for Enterprise AI at Snowflake Summit 2026 (AutoGraph + Virtual Graph preview)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260602127934/en/Arango-Showcases-Live-Contextual-Data-Layer-for-Enterprise-AI-at-Snowflake-Summit-2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arango unveils AutoGraph and previews a zero-egress Virtual Graph for Snowflake at Summit 2026, building a Live Contextual Data Layer for enterprise AI.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ataccama</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ataccama launches data products and joins Open Semantic Interchange to deliver trusted context for AI on Snowflake</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ataccama</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.ataccama.com/news/ataccama-launches-data-products-and-joins-open-semantic-interchange-to-deliver-trusted-context-for-ai-on-snowflake</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>At Summit 26, Ataccama launched data product capabilities with a Data Trust Index, served via MCP into Snowflake CoWork/CoCo, and joined OSI.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AtScale</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AtScale Announces Integration for Snowflake Semantic Views to Extend Governed Metrics to Power BI and Excel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260602266545/en/AtScale-Announces-Integration-for-Snowflake-Semantic-Views-to-Extend-Governed-Metrics-to-Power-BI-and-Excel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>At Summit 26, AtScale unveiled Snowflake Semantic Views XMLA Endpoint (private preview), extending governed Snowflake metrics to Power BI and Excel without data movement.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Blend360</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Blend Acquires In516ht, a Snowflake Elite Partner, Expanding Enterprise AI Capabilities Globally</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/blend-acquires-in516ht-a-snowflake-elite-partner-expanding-enterprise-ai-capabilities-globally-302788630.html</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>On Summit 26's opening day, Blend360 acquired In516ht, a Snowflake Elite Partner, expanding its data engineering and AI capabilities within the Snowflake ecosystem.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BlueCloud</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BlueCloud Named 2026 Snowflake CoCo Catalyst Partner of the Year - Services AMS Adoption</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/bluecloud-named-2026-snowflake-coco-catalyst-partner-of-the-year---services-ams-adoption-302788708.html</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>At Summit 26, BlueCloud was named 2026 Snowflake CoCo Catalyst Partner of the Year for driving the most Snowflake CoCo adoption across the Americas.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CDW named 2026 AMER Snowflake Resale Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CDW received the 2026 AMER Snowflake Resale Partner of the Year award, announced during Snowflake Summit 2026 in San Francisco.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Collibra</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Snowflake and Collibra Expand Integration to Bring Governed Business Context and Semantics Across the Snowflake AI Data Cloud</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/snowflake-and-collibra-expand-integration-to-bring-governed-business-context-and-semantics-across-the-snowflake-ai-data-cloud-302788532.html</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Announced at Summit 26: new bi-directional integration syncing Collibra governed metadata and OSI semantic models with Snowflake; preview now, broader GA Q3 2026.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cognizant wins 2026 Snowflake Partner Award; debuts JPMC Acquirer Foundation Model on Snowflake</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>At Summit 26 Cognizant earned a 2026 Snowflake Partner Award and, with JPMC, introduced an Acquirer Foundation Model data intelligence platform built on Snowflake.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cyera</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cyera + Snowflake: govern every agent, secure every dataset, move at the speed of AI</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cyera</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.cyera.com/blog/cyera-snowflake-move-at-the-speed-of-ai</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>At Summit 26 Cyera announced Snowflake Access Governance remediation (GA), Cortex AI agent discovery (preview), and natural-language risk analysis via Cortex Analyst.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DAS42</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DAS42 Named 2026 Marketing &amp; Advertising Snowflake Services Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260602338646/en/DAS42-Named-2026-Marketing-Advertising-Snowflake-Services-Partner-of-the-Year</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Announced at Summit 26, DAS42 won Snowflake's 2026 Marketing &amp; Advertising Services Partner of the Year for identity resolution and AI work on Snowflake.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dbt Labs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What we announced at Snowflake Summit and why it matters (Fivetran + dbt merger, dbt Core v2.0)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dbt Labs</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.getdbt.com/blog/what-we-announced-at-snowflake-summit-and-why-it-matters</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>At Summit 2026, dbt Labs and Fivetran became one company, unveiled dbt Core v2.0 alpha and dbt State; named 2026 Snowflake Data Integration Partner of the Year.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dltHub</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>dltHub named 2026 Startup Program Snowflake Product Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>dltHub (makers of open-source dlt Python library) won the 2026 Startup Program Snowflake Product Partner of the Year award; also launched its dltHub pro offering around Summit.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Elementum</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Elementum Named 2026 Snowflake Product Partner of the Year - Agentic Transformation</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>At Summit 2026 Elementum won 2026 Snowflake Product Partner of the Year for Agentic Transformation; Snowflake Ventures invested in its agentic AI platform; License Patrol native app on Marketplace.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>evolv Consulting</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>evolv Consulting Named 2026 AMER Snowflake Services Growth Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>evolv Consulting</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://evolv.consulting/evolv-consulting-snowflake-summit-2026-at-a-glance/</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>At Snowflake Summit 2026, evolv won 2026 AMER Snowflake Services Growth Partner of the Year and CoCo Catalyst Partner of the Year, with booth #1201 and two sessions.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Flexor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Flexor Announces Integration with Snowflake to Bring AI-Ready Unstructured Data Context into the Snowflake AI Data Cloud</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance (Business Wire)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/sectors/technology/articles/flexor-announces-integration-snowflake-bring-190000617.html</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>At Snowflake Summit 2026, Flexor unveiled native integration of its AI Context Engine (ACE) into Snowflake, turning unstructured data into AI-ready context; booth #2705.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Glean Technologies</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Snowflake in Glean Assistant now generally available; Glean named 2026 AMER Snowflake Product Innovation Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.glean.com/blog/query-snowflake-data-in-glean-assistant</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>GA of Snowflake as native data source in Glean Assistant via Cortex Analyst; Glean named 2026 AMER Snowflake Product Innovation Partner of the Year.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hightouch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Hightouch named 2026 Marketers and Advertisers Snowflake Product Partner of the Year at Summit 2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>At Snowflake Summit 2026, Hightouch won 2026 Marketers &amp; Advertisers Product Partner of the Year for its composable CDP and agentic marketing on Snowflake.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>IBM named a new Zero-Copy Integration partner and wins 2026 AMER Snowflake Services Innovation Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/news/press-releases/snowflake-pioneers-new-open-framework-for-interoperable-enterprise-data-and-ai/</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>At Summit 2026, Snowflake named IBM a new Zero-Copy Integration partner; IBM also won 2026 AMER Snowflake Services Innovation Partner of the Year.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Immuta</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Immuta Launches New Agentic Data Access Capabilities on Snowflake AI Data Cloud</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/immuta-launches-new-agentic-data-access-capabilities-on-snowflake-ai-data-cloud-302788954.html</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>At Summit 2026, Immuta launched agentic data access capabilities powered by Snowflake Cortex AI, governing AI-agent data access with zero standing privileges.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kumo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kumo Named 2026 Snowflake Product Partner of the Year for AI Tooling</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Snowflake named Kumo its 2026 Product Partner of the Year for AI Tooling, recognized at Snowflake Summit 26 partner awards.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Matia</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Matia Launches on Snowflake Marketplace, Bringing Unified Data Operations to the AI Data Cloud</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260602861670/en/Matia-Launches-on-Snowflake-Marketplace-Bringing-Unified-Data-Operations-to-the-AI-Data-Cloud</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>At Summit 26, Matia launched on Snowflake Marketplace, offering unified ETL, reverse ETL, observability, and catalog DataOps directly on Snowflake.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Merkle</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Merkle showcases Snowflake-native identity apps and MCP composable identity session at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Merkle</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.merkle.com/en/merkle-now/events/snowflake-summit.html</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>At Summit Booth #2527, Merkle (Snowflake Elite/Intelligence launch partner) demos Snowflake-native identity resolution and runs an MCP composable-identity session.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Microsoft OneLake and Snowflake interoperability is now generally available, including a Snowflake item in OneLake</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Blog</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://blog.fabric.microsoft.com/en-US/blog/microsoft-onelake-and-snowflake-interoperability-is-now-generally-available/</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>At Summit 26, OneLake-Snowflake Iceberg interoperability reached GA, a Snowflake-branded OneLake item entered preview, plus deeper Microsoft Foundry integration.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Monte Carlo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Monte Carlo named 2026 Data Governance Snowflake Product Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.manilatimes.net/2026/06/03/tmt-newswire/globenewswire/monte-carlo-named-2026-data-governance-snowflake-product-partner-of-the-year/2357274</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>At Summit 2026, Snowflake named Monte Carlo Data Governance Product Partner of the Year for its data and AI observability across Cortex Agents.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NTT DATA is Blue Square sponsor at Snowflake Summit 2026 with Federated AI Mesh demo and two 2026 Snowflake Partner Awards</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://us.nttdata.com/en/events/2026/june/snowflake-summit-2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Booth #1202 demos and a breakout session; with Mitsui builds a Snowflake 'Federated AI Mesh'; won two 2026 Snowflake APJ partner awards.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>phData</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>phData Named 2026 Global Snowflake Services AI Partner of the Year and 2026 AMER Snowflake Services Implementation Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ACCESS Newswire</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>phData won two Snowflake Partner of the Year awards at Summit 26, its seventh consecutive year, spotlighting a Cortex-based Data Modeling Agent.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Posit</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Posit Wins Two Snowflake Partner of the Year Awards for Data Science</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PRWeb</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.prweb.com/releases/posit-wins-two-snowflake-partner-of-the-year-awards-for-data-science-302788999.html</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Posit won Global Product Innovation and AI/ML Data Science Tooling Partner of the Year at Summit 26 for its R/Python Native App on Snowflake.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>RelationalAI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RelationalAI Closes the AI Value Gap with New Agentic Decision Intelligence Capabilities for the Snowflake AI Data Cloud</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.manilatimes.net/2026/06/03/tmt-newswire/globenewswire/relationalai-closes-the-ai-value-gap-with-new-agentic-decision-intelligence-capabilities-for-the-snowflake-ai-data-cloud/2357275</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>At Snowflake Summit 26, RelationalAI launched the Rel App plus prescriptive/predictive reasoners, Snowflake CoWork conversational decision intelligence, and push-button post-training, native to Snowflake.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Retool</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Snowflake CoCo adds Retool integration to build AI apps on governed Snowflake data</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/news/press-releases/snowflake-coco-redefines-enterprise-ai-development-as-the-coding-agent-built-for-faster-easier-and-more-powerful-innovation-anywhere/</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>At Summit 26, Snowflake's CoCo coding agent gains a Retool integration so teams build AI-powered apps on governed Snowflake data.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RudderStack</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RudderStack launches RudderAI at Snowflake Summit 26</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/rudderstack-launches-rudderai-to-help-snowflake-customers-drive-measurable-results-from-their-customer-data-302784552.html</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>RudderAI suite of CLI, MCP tools and five agents for agentic customer-data workflows on Snowflake, launched at Summit 26.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Snowflake open framework adds Salesforce zero-copy and MCP integrations</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/news/press-releases/snowflake-pioneers-new-open-framework-for-interoperable-enterprise-data-and-ai/</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Summit 26 framework lets Salesforce data be accessed without replication via Zero-Copy Integrations and Model Context Protocol connectors.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sigma</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sigma Named 2026 Business Intelligence Snowflake Product Partner of the Year and 2026 EMEA Snowflake Product Growth Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260602857603/en/Sigma-Named-2026-Business-Intelligence-Snowflake-Product-Partner-of-the-Year-and-2026-EMEA-Snowflake-Product-Growth-Partner-of-the-Year</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>At Summit 2026 Sigma won 2026 BI Snowflake Product Partner of the Year (fourth straight year) and EMEA Product Growth Partner of the Year.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Slalom</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Slalom named 2026 Global Snowflake Services Innovation Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>At Summit 2026 Slalom won Global Services Innovation Partner of the Year; present at Booth #1109 with a Capital One Iceberg migration session.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Spaulding Ridge</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Spaulding Ridge Named 2026 Media &amp; Entertainment Snowflake Services Partner of the Year at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Spaulding Ridge</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Spaulding Ridge sponsors Summit 2026 with live Openflow accelerator and CoCo/Snowflake Intelligence demos; recognized as 2026 Media &amp; Entertainment Services Partner of the Year.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ThoughtSpot</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ThoughtSpot Expands Governed Enterprise AI with Snowflake Cortex AI and Semantic Views</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/06/02/3305548/0/en/ThoughtSpot-Expands-Governed-Enterprise-AI-with-Snowflake-Cortex-AI-and-Semantic-Views.html</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>At Summit 26, ThoughtSpot integrates Spotter and its agents with Snowflake Cortex Analyst/Agents and Semantic Views, adding Cortex visualizations and BYO-LLM.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TransUnion</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TransUnion Named 2026 Media and Entertainment Snowflake Product Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>TransUnion Newsroom</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://newsroom.transunion.com/transunion-named-2026-media-and-entertainment-snowflake-product-partner-of-the-year/</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>TransUnion won Snowflake's 2026 Media &amp; Entertainment Product Partner of the Year award at Summit 26 for identity resolution solutions on Snowflake.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tredence</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tredence Named 2026 Retail &amp; Consumer Goods Snowflake Services Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/tredence-named-2026-retail--consumer-goods-snowflake-services-partner-of-the-year-2026-for-the-second-consecutive-year-302787067.html</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tredence won Snowflake's 2026 Retail &amp; CG Services Partner of the Year for the second year; showcased IRIS agentic framework at Summit Booth #2417.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TrustLogix</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TrustLogix Launches TrustAI Integration with Snowflake AI Data Cloud</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PRWeb</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.prweb.com/releases/trustlogix-launches-trustai-integration-with-snowflake-ai-data-cloud-bringing-scalable-agentic-ai-data-security-to-enterprise-teams-302788964.html</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>TrustLogix launched TrustAI for Snowflake Cortex AI, governing agent/tool access, plus TrustAI Guardian and a free Data Security Scanner on Snowflake Marketplace.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Workato</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Workato at Snowflake Summit 2026: Data Orchestration to Activation with Enterprise MCP &amp; Agentic AI</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Workato</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://mktg.workato.com/Snowflake-Summit.html</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Workato runs a Summit session (Tue June 2, booth #1108) on making Snowflake data AI-ready via secure, governed MCP servers and agents.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Coalesce</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Coalesce hosts joint demo at Snowflake Summit 2026 (Booth 1204) on unified DataOps + transformation</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Coalesce</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://coalesce.io/events/snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Coalesce exhibits at Booth 1204 and runs a June 2 joint demo showing move, monitor and activate data on Snowflake with its transformation layer.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Insider One</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Insider One launches Zero Copy Segmentation for Snowflake</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Insider One</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://insiderone.com/zero-copy-segmentation-snowflake/</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Insider One launched Zero Copy Segmentation, a native Snowflake integration letting marketers build and activate audiences from Snowflake data without copying it.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Kipi.ai</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>kipi.ai named 2026 Telecom Snowflake Services Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>At Summit 2026, Snowflake named kipi.ai (part of Capgemini) the 2026 Telecom Snowflake Services Partner of the Year among its partner award winners.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>OneSix</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>OneSix recognized as a CoCo global partner during the Snowflake Summit 26 Platform Keynote</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>OneSix</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://onesix.ai</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>OneSix exhibited at Summit 26 (booth 2304) and was named a Snowflake CoCo global partner during the Platform Keynote following its onesix.ai rebrand.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Estuary</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Estuary showcases real-time Snowflake data integration at Snowflake Summit 2026 (Booth 1204)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Estuary</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://estuary.dev/source/snowflake/</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Estuary exhibited at Snowflake Summit 2026 (Booth 1204), demoing real-time CDC/ETL pipelines that move data into Snowflake without batch-vs-streaming tradeoffs.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hevo Data</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Hevo Data hosts data-leader wind-down event at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/summit/partner-events/</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hevo, with Prolim and Lightdash, hosts an exclusive Snowflake Summit 2026 evening event for data and analytics leaders at Hilton SF.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Capital One Software</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Capital One Software announces new observability and AI-powered optimization capabilities for Slingshot</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260601466677/en/Capital-One-Software-Announces-New-Observability-and-AI-Powered-Optimization-Capabilities-for-Slingshot-to-Drive-System-Wide-Data-Efficiency</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Slingshot gains context-aware query optimization, duplicate pipeline detection and a Data Explorer to drive system-wide Snowflake cost and performance efficiency.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Fivetran + dbt Labs Complete Merger to Create the Data Infrastructure for Trusted AI Agents</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Fivetran</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.fivetran.com/press/fivetran-dbt-labs-complete-merger-to-create-the-data-infrastructure-for-trusted-ai-agents</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fivetran closed its dbt Labs merger on June 1, 2026, timed to Snowflake Summit, debuting combined agentic-workflow and orchestration innovations plus dbt Core v2.0; booth #2313.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FalkorDB</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>FalkorDB exhibits Snowflake-native graph engine at Snowflake Summit 2026 (Lodge Booth 2719)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FalkorDB</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.falkordb.com/blog/falkordb-on-snowflake-graph-database/</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>FalkorDB was a Lodge Partner at Snowflake Summit 2026 (Booth 2719), showcasing its Snowflake Native App that turns warehouse tables into Cypher-queryable knowledge graphs for GraphRAG.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Meta Integration</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Meta Integration Technology sponsors Snowflake Summit 2026, demos MetaKarta Semantic Hub for Snowflake Cortex</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MetaKarta (Meta Integration Technology)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.metakarta.com/event-details/snowflake-summit-25-1</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Summit 2026 sponsor demoing MetaKarta Semantic Hub as a governed semantic control plane that brings consistent business meaning to Snowflake Cortex AI.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Revefi</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Revefi showcases AI FinOps and AI Data Engineer at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Revefi</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.revefi.com/offline-event/join-revefi-at-snowflake-summit-2026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Revefi exhibits at booth 1410, demoing its AI agent for Snowflake cost optimization, performance and data quality at Summit 26.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Seemore Data</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Seemore Data runs $5,000 Snowflake savings challenge at Summit 2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Seemore Data</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://seemoredata.io/blog/5000-challenge/</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>At Summit 26 booth #2521, Seemore offers a challenge: cut Snowflake costs 20%+ or pay $5,000; promotion runs through June 2026.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FreedomPay</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>FreedomPay showcases payment orchestration and Snowflake partnership at Snowflake Summit 2026 (Booth 2612)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>FreedomPay</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://corporate.freedompay.com/about-us/events/snowflake-summit-26</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>FreedomPay exhibited at Snowflake Summit 2026 (Booth 2612), highlighting its payment orchestration platform and partnership with Snowflake.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Hexaware</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Hexaware at Snowflake Summit 2026 (Booth #2419) showcasing Amaze for Data and AI</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Hexaware</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://hexaware.com/event/snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hexaware at Snowflake Summit 2026 Booth #2419, showcasing BI-to-AI-ready data journeys and its Amaze Snowflake migration and optimization solutions.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MessageGears</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MessageGears hosts 'Turn your warehouse into your marketing engine' session at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>MessageGears</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://messagegears.com/blog/what-were-looking-forward-to-at-the-snowflake-summit/</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Warehouse-native ESP MessageGears is at Summit 2026 promoting direct Snowflake activation; also named 'one to watch' in Snowflake's Modern Marketing Data Stack report.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Braze named Snowflake 2026 APJ Product Growth Partner of the Year; launches user profile streaming for Snowflake</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.braze.com/resources/articles/braze-snowflake-customer-intelligence</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Braze won a 2026 Snowflake Partner Award and introduced real-time user profile streaming to Snowflake for a 360-degree customer view.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Capgemini named 2026 EMEA Snowflake Services Innovation Partner of the Year</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/2026-summit-partner-awards/</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>At Summit 2026 Snowflake named Capgemini EMEA Services Innovation Partner of the Year; its kipi.ai unit won Telecom Services Partner of the Year.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Prefect Technologies</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Prefect Launches Workflow Orchestration Offering on Snowflake Marketplace</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BigDATAwire</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.tipranks.com/news/private-companies/prefect-launches-workflow-orchestration-offering-on-snowflake-marketplace</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Prefect partnered with Snowflake, listing its workflow orchestration on Snowflake Marketplace and connecting AI agents to Snowflake via FastMCP and Horizon MCP Gateway.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sifflet</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sifflet brings end-to-end data observability and AI agents to Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Sifflet</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.siffletdata.com/webinars-and-replays/meet-us-at-the-snowflake-summit-2026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sifflet exhibits at Booth #1507, highlighting column-level lineage and three AI observability agents acting as a control plane for Snowflake data.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Snowplow</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Snowplow named a Leader in Snowflake's 2026 Modern Marketing Data Stack Report</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Snowplow</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://snowplow.io/blog/snowflake-2026-modern-marketing-data-stack-report</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Snowplow named a Leader in Snowflake's 2026 Modern Marketing Data Stack Report for a second year; partnership expanded via Snowplow Signals on Snowflake.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7Rivers</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>7Rivers at Snowflake Summit 2026 with live Snowflake Intelligence demos and June 2 networking reception</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>7Rivers</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://7riversinc.com/events-and-webinars/snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Snowflake data consultancy 7Rivers exhibits at Summit 2026 showing Snowflake Intelligence and data agents, plus a June 2 happy-hour reception for data leaders.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Acceldata showcases data observability for Snowflake at Summit 2026 (booth #1607)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Acceldata</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.acceldata.io/events/snowflake-summit-2026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Acceldata exhibits its multidimensional data observability platform for Snowflake at Summit 2026 booth #1607, covering anomaly detection, reliability and spend forecasting.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Acxiom</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Acxiom named customer partner for Snowflake Horizon Catalog AI security at Summit 2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/news/press-releases/snowflake-advances-trusted-ai-with-snowflake-horizon-catalog-centralizing-governance-context-and-security-across-the-enterprise/</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Acxiom highlighted alongside NewDay and Thomson Reuters in Snowflake's Summit 2026 Horizon Catalog launch, exploring new AI security and governance for agentic systems.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Airbyte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Airbyte named Integration leader in Snowflake's Modern Marketing Data Stack 2026, partner at Summit 2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/airbyte-recognized-leader-snowflake-modern-170000552.html</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Airbyte recognized as an Integration leader in Snowflake's Modern Marketing Data Stack 2026 report and participates as a partner at Snowflake Summit 2026.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Altimate AI</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Altimate AI CEO speaks at Snowflake Summit 2026 on why production AI agents fall short</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Altimate AI</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.altimate.ai/</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Co-founder/CEO Pradnesh Patil presents at Snowflake Summit 2026 on context, governance and infrastructure gaps; Altimate's agentic data-engineering platform supports Snowflake.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Amperity</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Amperity at Snowflake Summit 2026 (booth #1317) on unified customer data for AI</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Amperity</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://amperity.com/events/snowflake-summit-2026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Amperity exhibits at Snowflake Summit 2026 booth #1317, showing how unified customer data on Snowflake powers AI, analytics and personalized engagement.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Astronomer at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Astronomer</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.astronomer.io/events/snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Astronomer presents Summit 2026 sessions on Apache Airflow unifying data pipelines and AI workflows, plus runtime governance and a networking takeover event.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Atlan</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Join Atlan at Snowflake Summit 2026 | Booth #1612</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Atlan</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://atlan.com/event/snowflake-summit/</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Atlan showcases its open context layer at Summit 2026 booth #1612, giving AI agents and Snowflake Cortex governed business context for production use.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CARTO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CARTO brings agentic GIS to Snowflake using Cortex Code</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CARTO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://carto.com/blog/agentic-gis-snowflake-cortex-code-carto/</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>CARTO details agentic geospatial analysis in Snowflake via Cortex Code, extending its Snowflake Native App spatial analytics around Summit 2026.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CData</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CData at Snowflake Summit 2026 (booth #2738) showcasing Sync and Connect AI for Cortex agents</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>CData</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.cdata.com/blog/snowflake-summit-2026-guide</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>CData exhibits at Summit 2026, demoing CData Sync into Snowflake and Connect AI giving Cortex agents live, governed access to external sources.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Chalk</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Chalk makes Snowflake Summit 2026 debut with real-time feature store deep dive</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Chalk</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://chalk.ai/events/snowflake-summit-2026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Chalk's first Summit appearance (booth #2611); co-founder Elliot Marx presents building a real-time feature store with sub-5ms inference in Snowflake.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Domo showcases Snowflake Native App and Cortex-powered Marketing Mix Modeling at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.domo.com/events/attend-snowflake-summit-26-with-domo---booth-1610</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>At Summit 2026 (booth #1610) Domo demoed a production Marketing Mix Modeling solution with a Snowflake Native App fully integrated into Cortex AI.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>DQLabs</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Meet DQLabs at Snowflake Summit 2026, Booth #2739 - See PRIZM Live</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DQLabs</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.dqlabs.ai/events/snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DQLabs presents PRIZM, its AI-native data quality and observability platform on Snowflake, at Summit 2026 booth #2739, demoing anomaly detection and automated remediation.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Honeydew</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Honeydew integrates its semantic layer with Snowflake Semantic Views; Snowflake Native App at Summit 2026 Booth #2412</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Honeydew</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://honeydew.ai/blog/honeydew-and-snowflake-semantic-views/</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Honeydew extends its semantic layer onto Snowflake's new Semantic Views (Cortex semantic models), available as a Snowflake Native App; exhibiting at Summit 2026.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Infosys Topaz at Snowflake Summit 2026 (Booth #1315)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.infosys.com/newsroom/events/2026/snowflake-summit-2026.html</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Infosys showcases Topaz AI offerings and agentic AI solutions built on Snowflake at Summit 2026 via sessions and booth presence.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Mastek</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mastek showcases Snowflake-native Galaxy Suite at Snowflake Summit 2026 (Booth 2614)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Mastek</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.mastek.com/events/snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Mastek exhibits at Summit 26 booth 2614, showcasing its Snowflake-native Galaxy Suite for data modernization, Cortex analytics, and enterprise AI products.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pantomath</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pantomath deepens Snowflake AI Data Cloud integration, exhibits at Snowflake Summit 2026 (Booth 2307)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Pantomath</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.pantomath.com/</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Data observability vendor at Summit 26 booth 2307, deepening Snowflake AI Data Cloud integration alongside a Snowflake Ventures investment and AI DRE Agent.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PointFive</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PointFive brings DeepWaste detection and Warehouse Optimization for Snowflake to Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PointFive</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.pointfive.co/events/snowflake-summit</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cloud-efficiency vendor at Summit 26 showcasing DeepWaste for Data Platforms and Snowflake Warehouse Optimization with agentic remediation of cost issues.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Precisely at Snowflake Summit 26: Closing the Agentic AI Data Integrity Gap</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Precisely</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.precisely.com/blog/data-integrity/precisely-at-snowflake-summit-26-closing-the-agentic-ai-data-integrity-gap/</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Data-integrity vendor at Summit 26 booth 1212 with a June 2 session on preparing Snowflake data for agentic AI ROI via accuracy, enrichment, and governance.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Wipro Limited</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Meet Wipro at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.wipro.com/events/meet-wipro-at-snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Wipro sponsored Summit 26, showcasing agentic AI via WEGA and Snowflake Cortex AI plus client use cases across supply chain, financial services and healthcare.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Alation</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Alation at Snowflake Summit 2026 (booth #1303) with attendee session guide</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Alation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.alation.com/blog/snowflake-summit-2026-guide/</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alation exhibits at Snowflake Summit 2026 booth #1303 and publishes a guide to dates, keynotes and sessions for the governed agentic-AI theme.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Alteryx</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Alteryx at Snowflake Summit 2026 showing in-Snowflake analytics with built-in governance</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Alteryx</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.alteryx.com/events</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alteryx joins Snowflake Summit 2026 to demonstrate AI-driven analytics running directly inside Snowflake without moving data, with governance built in.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>DataOps.live</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DataOps.live hosts partner event at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/summit/partner-events/</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>DataOps.live is a partner-hosted event sponsor at Snowflake Summit 2026 (drinks/food at The Chieftain Irish Pub); ongoing Snowflake Native App and Cortex partnership.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Reltio</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Reltio at Snowflake Summit 2026 (sponsor/booth presence)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Reltio</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://www.reltio.com/resources/events/snowflake-summit/</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Reltio is a Snowflake Summit 26 sponsor (June 1-4, San Francisco), showcasing Reltio Data Cloud for unifying data/metadata into trusted 360 views for AI agents. No product launch.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DataHub</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DataHub launches DataHub Cloud release giving analytics agents trusted context, showcased at Snowflake Summit</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DataHub</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://datahub.com/news/datahub-launches-breakthrough-release-that-gives-analytics-agents-trusted-context-pushing-accuracy-levels-beyond-90/</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>DataHub Cloud adds a context layer for agents like Snowflake Intelligence to push accuracy past 90%; showcased at Snowflake Summit 26 (Booth 1309).</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Gray Swan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Gray Swan raises $40M Series A with Snowflake Ventures; runtime AI protection integrated natively into Snowflake</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Gray Swan</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.grayswan.ai/news/gray-swan-announces-series-a</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Snowflake Ventures backed Gray Swan's $40M Series A; partnership embeds Gray Swan's runtime AI security natively into Snowflake's AI ecosystem.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Unravel Data</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Unravel Data Launches Arvix AI to Autonomously Optimize Databricks, Snowflake and BigQuery</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>BigDATAwire</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.hpcwire.com/bigdatawire/this-just-in/unravel-data-launches-arvix-ai-to-autonomously-optimize-databricks-snowflake-and-bigquery/</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Unravel unveiled Arvix AI, an agentic engine that autonomously tunes and optimizes Snowflake (and Databricks/BigQuery) workloads, days before Summit 26.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Snowflake Expands AWS Collaboration with $6B Commitment to Accelerate Enterprise Agentic AI Adoption</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/news/press-releases/snowflake-expands-aws-collaboration-with-6b-commitment-to-accelerate-enterprise-agentic-ai-adoption/</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ahead of and demonstrated at Summit 26, Snowflake and AWS expanded their collaboration with a $6B Snowflake infrastructure commitment to accelerate enterprise agentic AI.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Hex</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Hex featured as customer in Snowflake's $6B AWS collaboration expansion at Summit 2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/news/press-releases/snowflake-expands-aws-collaboration-with-6b-commitment-to-accelerate-enterprise-agentic-ai-adoption/</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hex CTO Caitlin Colgrove quoted in Snowflake's expanded $6B AWS agentic-AI collaboration; Hex relies on Snowflake on AWS for governed enterprise AI.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Informatica</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Informatica Brings Headless Data Management and Iceberg Governance to Snowflake</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Informatica</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.informatica.com/about-us/news/news-releases/2026/05/20260520-informatica-brings-headless-data-management-and-iceberg-governance-to-snowflake.html</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Informatica unveiled Headless IDMC for Cortex AI agents, GA row-level access governance, and Iceberg table scanners for Snowflake ahead of Summit 2026.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AVEVA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AVEVA and Snowflake Forge Strategic Collaboration to Accelerate Industrial AI and Unify IT/OT Data Ecosystems</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AVEVA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.aveva.com/en/about/news/press-releases/2026/aveva-and-snowflake-forge-strategic-collaboration-to-accelerate-industrial-ai-and-unify-it-ot-data-ecosystems/</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>AVEVA and Snowflake announced a zero-copy integration between CONNECT and Snowflake, demonstrated at Summit 26, unifying IT/OT data for industrial AI.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DataRadar</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DataRadar Expands Platform with Native Data Quality and Cost Optimization App on Snowflake Marketplace</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/dataradar-expands-platform-with-native-data-quality-and-cost-optimization-app-on-snowflake-marketplace-302776436.html</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>DataRadar launched a Snowflake native app for data quality and cost optimization on the Marketplace, running inside customers' Snowflake; meeting attendees at Summit 2026.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Dataiku</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Dataiku Launches Cobuild on Snowflake: From Prompt to Production-Ready AI Workflow, Inside Snowflake</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20260515379743/en/Dataiku-Launches-Cobuild-on-Snowflake-From-Prompt-to-Production-Ready-AI-Workflow-Inside-Snowflake</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dataiku launched Cobuild on Snowflake, turning natural-language prompts into governed AI workflows and agents inside Snowflake using Cortex models; also named 2026 Snowflake AI Platform Partner of the Year.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tealium</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Tealium Launches Audience Discovery for Snowflake as a Native App to Power Real-Time Customer Activation</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Tealium</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://tealium.com/press-releases/audience-discovery-snowflake/</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tealium Audience Discovery for Snowflake, a Native App letting customers build/govern/activate audiences in-place; on Snowflake Marketplace in Q2. Booth #1414 at Summit.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SAP and Snowflake reach GA on bidirectional zero-copy integration for enterprise AI</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/blog/sap-snowflake-zero-copy-integration-enterprise-ai/</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SAP Business Data Cloud Connect for Snowflake reaches GA with bidirectional zero-copy SAP data integration; reaffirmed at Summit 26.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Perficient</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Your Data is Ready, Your AI Can Be Too: Perficient at Snowflake Summit 2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Perficient</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://blogs.perficient.com/your-data-is-ready-your-ai-can-be-too-perficient-at-snowflake-summit-2026/</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Snowflake Premier and Cortex Code Preferred Partner at Summit 26 booth 2422 with live Cortex Code demos across financial services, retail, manufacturing, and healthcare.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Boomi</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Boomi Agent Control Tower adds Snowflake Cortex provider; Unified Server Catalog ingests Snowflake MCP servers</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Boomi</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://boomi.com/blog/boomi-innovations-may-2026/</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Boomi, a Snowflake Elite Partner at Summit 2026, adds Snowflake Cortex as an Agent Control Tower provider and surfaces Snowflake MCP servers in its catalog.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tealium</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Tealium recognized in Snowflake's 2026 Modern Marketing Data Stack for powering real-time engagement via bi-directional data flows</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Tealium</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://tealium.com/press-releases/2026-modern-marketing-data-stack/</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Tealium named to Snowflake's 2026 Modern Marketing Data Stack report for enabling real-time, bi-directional customer data flows with Snowflake.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GrowthArc</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>GrowthArc earns Snowflake Cortex Code Preferred Partner Badge for 2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AiThority</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://aithority.com/machine-learning/growtharc-earns-snowflake-cortex-code-preferred-partner-badge/</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>GrowthArc among select global partners awarded Snowflake's Cortex Code Preferred Partner Badge; also hosting a Snowflake Summit 2026 sidelines dinner.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OneTrust</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>OneTrust embeds consent signals into Snowflake Data Clean Rooms for consent-aware data collaboration</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/04/28/3282829/0/en/onetrust-introduces-a-new-approach-to-consent-aware-data-clean-rooms.html</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>OneTrust's 2026 Snowflake collaboration embeds consent signals into Snowflake Data Clean Rooms, making user consent enforceable across multi-party data collaboration.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sparq</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Sparq achieves Snowflake Elite Partner status for AI Data Cloud Services</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Sparq</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.teamsparq.com/insights/sparq-achieves-snowflake-elite-status/</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Sparq reached Snowflake's Elite Partner tier in 2026, building workloads inside Cortex, Native Apps and ML; also launched Sparq Intelligence Studio in February.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Sundial</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sundial Joins Snowflake &amp; Industry Leaders to Support Data + AI Interoperability Through the Open Semantic Interchange</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>SalesTechStar</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://salestechstar.com/partner-management-channel-enablement/sundial-joins-snowflake-industry-leaders-to-support-data-ai-interoperability-through-the-open-semantic-interchange/</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Sundial joins Snowflake-led Open Semantic Interchange (OSI), an open, vendor-neutral semantic-model spec standardizing data definitions across BI, AI and governance tools.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Matillion</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Matillion Launches Maia's Migration Agent: Autonomous Migration for Legacy ETL Platforms</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/matillion-launches-maias-migration-agent-autonomous-migration-for-legacy-etl-platforms-302726632.html</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Matillion's new Maia Migration Agent autonomously converts legacy ETL pipelines into native, warehouse-optimized pipelines on Snowflake, Databricks, and Redshift.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TEKSystems Global Services</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>TEKsystems Global Services Partners With Snowflake To Accelerate AI-Driven Energy Solutions</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>TEKsystems</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://www.teksystems.com/en/insights/newsroom/2026/snowflake-energy-launch</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>TEKsystems Global Services named a Snowflake Energy Solutions Launch Partner to help oil, gas, power and utilities modernize with AI-powered insights.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Snowflake and OpenAI Forge $200 Million Partnership to Bring Enterprise-Ready AI to the World's Most Trusted Data Platform</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/news/press-releases/snowflake-and-openAI-forge-200-million-partnership-to-bring-enterprise-ready-ai-to-the-worlds-most-trusted-data-platform/</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Multi-year $200M partnership making OpenAI frontier models natively available in Snowflake Cortex AI; co-developing agents over governed data, spotlighted at Summit 26.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hakkoda (an IBM Company)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Hakkoda partners with Snowflake to launch Snowflake's Energy Solutions for AI-driven energy operations</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Hakkoda</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://hakkoda.io/resources/ai-driven-energy-operations/</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hakkoda and Snowflake collaborate to launch Snowflake Energy Solutions, unifying IT/OT/IoT data and applying AI for oil, gas, power and utilities.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Google Cloud</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Snowflake brings Google's Gemini 3 to Snowflake Cortex AI, expanding partnership</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.snowflake.com/en/news/press-releases/snowflake-enables-enterprise-ready-ai-by-bringing-google-s-gemini-3-to-snowflake-cortex-ai/</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Gemini 3 natively available in Snowflake Cortex AI; expanded go-to-market alignment, co-sell, and Google Cloud Marketplace transactability.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="130" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Snowflake Summit 2026 - Partner Scouting Dashboard | Build &amp; Methodology Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>HOW TO READ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>197 Snowflake Summit 2026 partner vendors scored on five 0-10 dimensions, blended into an Overall Score and a Priority Tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Priority Tier is a scouting-priority call (A = must-see) - editorial, NOT a strict score cutoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Magic Quadrant: Ability to Execute (Y) = mean(Snowflake, Retail/Customer); Completeness of Vision (X) = mean(AI, IPO/Upside). The cross sits at the cohort average -&gt; Leaders / Challengers / Visionaries / Niche Players.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Summit News tab: live partner announcements gathered per vendor, categorised into buckets (Awards / Launches / Integrations / Partnerships / Events &amp; Booths / M&amp;A / Other).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CALCULATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Overall Score = mean(Snowflake, AI, Retail/Customer, IPO/Upside, Bryan-Fit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Priority Tier guide = A &gt;= 7.5 . B &gt;= 6.0 . C &lt; 6.0  (tiers are editorial / Bryan's curation, not a hard cutoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Ability to Execute = mean(Snowflake Score, Retail-Customer Score)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Completeness of Vision = mean(AI Score, IPO/Upside Score)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Magic-Quadrant cross = cohort average of each axis (re-centred per niche on drill-down)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ASSUMPTIONS &amp; CAVEATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Directional scouting scores in Bryan's lens - NOT an official Gartner Magic Quadrant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>70 vendors originally carried placeholder scores; rescored via AI web research over two passes, reconciled. Two remain low-confidence (edata, Integrated Quantum Technologies); Bryan-Fit is an estimate to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Public market caps researched; many private funding / valuation figures still need validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Summit News is AI-gathered from public news / press; links go to the primary source - directional, verify before relying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>DATA SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Primary: this workbook (Master Directory) -&gt; vendors.json, the 197-partner directory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rescore research: company sites, funding/valuation data (Crunchbase / PitchBook-style), Snowflake partner directory &amp; Summit materials, press/funding announcements - gathered by AI research agents, reconciled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Summit News: per-vendor public news/press searches (Snowflake newsroom, PR Newswire, Business Wire, GlobeNewswire, vendor event pages), deduped + link-checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Charting: Chart.js 4.4.1 (vendored, MIT). Build: build.py (Python) -&gt; dashboard.html; GitHub Pages serves /summit/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Generated 2026-06-03  |  197 vendors  |  108 news announcements</t>
         </is>
       </c>
     </row>
